--- a/stories/arbres/TREE-VIV-004.xlsx
+++ b/stories/arbres/TREE-VIV-004.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Kenzo est près de la fenêtre, avec papa. Une petite plante est là. Les feuilles sont sèches. Papa dit : la plante a besoin d'eau. Elle a besoin de lumière. On arrose avec un adulte. Papa tient le petit arrosoir. Kenzo aide, tout doux. L'eau coule. La lumière entre. La plante a besoin d'eau et de lumière, avec un adulte.</t>
+          <t>Kenzo est près de la fenêtre, avec papa. Une petite plante est là. Les feuilles sont sèches. La plante a besoin d'eau. Elle a besoin de lumière. On arrose avec un adulte. Papa tient le petit arrosoir. Kenzo aide, tout doux. L'eau coule. La lumière entre. La plante a besoin d'eau et de lumière, avec un adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo est près de la fenêtre, avec papa. Une petite plante est là. Les feuilles sont sèches.
+papa|La plante a besoin d'eau. Elle a besoin de lumière. On arrose avec un adulte. Papa tient le petit arrosoir.
+narrateur|Kenzo aide, tout doux. L'eau coule. La lumière entre. La plante a besoin d'eau et de lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1540,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Kenzo pose les cubes près de la plante. Papa dit : eau, lumière, avec un adulte. Kenzo touche la terre. Elle est sèche. On arrose avec papa. La plante a besoin d'eau et de lumière, avec un adulte.</t>
+          <t>Kenzo pose les cubes près de la plante. Eau, lumière, avec un adulte. Kenzo touche la terre. Elle est sèche. On arrose avec papa. La plante a besoin d'eau et de lumière, avec un adulte.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1678,13 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo pose les cubes près de la plante.
+papa|Eau, lumière, avec un adulte.
+narrateur|Kenzo touche la terre. Elle est sèche. On arrose avec papa. La plante a besoin d'eau et de lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1861,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|La plante a soif. On fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2034,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a arrosé, avec un adulte. Eau. Lumière. La plante a besoin d'eau et de lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2229,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2396,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend une pomme. Un vélo passe, toc toc. Kenzo pose une pomme près de la plante. L'eau a coulé. La lumière reste. Avec un adulte. La plante a besoin d'eau et de lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2587,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2754,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chat. La lumière est claire. On range la chaise. On a arrosé. Eau et lumière, avec un adulte. La terre est humide. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2921,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3088,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chien. Des miettes dorment sur la table. On range un objet. On a arrosé. Eau et lumière, avec un adulte. La fenêtre donne la lumière. La plante a besoin d'eau et de lumière, avec un adulte. Papa serre Kenzo tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3255,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3422,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de la poule. Un chat miaule une fois. On se tient la main. On a arrosé. Eau et lumière, avec un adulte. L'arrosoir est rangé. La plante a besoin d'eau et de lumière, avec un adulte. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3589,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3756,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un yaourt. Le banc est lisse. Un yaourt attend. Kenzo regarde la terre humide. Eau, lumière, adulte. La plante a besoin d'eau et de lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3947,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3875,7 +3976,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Kenzo s'approche de le chat. Les chaussures font toc toc. On dit merci. On a arrosé. Eau et lumière, avec un adulte. La feuille est plus douce. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo range. Papa dit : c'est bien.</t>
+          <t>Kenzo s'approche de le chat. Les chaussures font toc toc. On dit merci. On a arrosé. Eau et lumière, avec un adulte. La feuille est plus douce. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo range. C'est bien.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4013,6 +4114,12 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chat. Les chaussures font toc toc. On dit merci. On a arrosé. Eau et lumière, avec un adulte. La feuille est plus douce. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4282,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4449,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chien. La couverture est douce. On souffle doucement. On a arrosé. Eau et lumière, avec un adulte. La terre est humide. La plante a besoin d'eau et de lumière, avec un adulte. On souffle. Kenzo sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4616,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4661,6 +4783,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de la poule. Une cloche tinte au loin. On écoute jusqu'au bout. On a arrosé. Eau et lumière, avec un adulte. La fenêtre donne la lumière. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4950,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4847,7 +4979,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Kenzo prend un morceau de pain. Les chaussures font toc toc. Un morceau de pain. Kenzo dit : encore un peu d'eau, avec papa. La lumière est là. La plante a besoin d'eau et de lumière, avec un adulte.</t>
+          <t>Kenzo prend un morceau de pain. Les chaussures font toc toc. Un morceau de pain. Encore un peu d'eau, avec papa. La lumière est là. La plante a besoin d'eau et de lumière, avec un adulte.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -4985,6 +5117,13 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un morceau de pain. Les chaussures font toc toc. Un morceau de pain.
+enfant-m|Encore un peu d'eau, avec papa.
+narrateur|La lumière est là. La plante a besoin d'eau et de lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5310,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5477,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chat. Le bois sent le chaud. On attend son tour. On a arrosé. Eau et lumière, avec un adulte. L'arrosoir est rangé. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5644,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5811,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chien. Une goutte tombe, ploc. On sourit ensemble. On a arrosé. Eau et lumière, avec un adulte. La feuille est plus douce. La plante a besoin d'eau et de lumière, avec un adulte. Papa serre Kenzo tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5978,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6145,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de la poule. Le savon sent la fleur. On pose les pieds par terre. On a arrosé. Eau et lumière, avec un adulte. La terre est humide. La plante a besoin d'eau et de lumière, avec un adulte. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6312,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6305,6 +6479,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo ouvre le livre des plantes. Une image verte. Papa montre la fenêtre. La lumière. Puis l'eau, avec un adulte. Kenzo écoute. La plante a besoin d'eau et de lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6481,6 +6660,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|La plante a besoin de quoi, près de la fenêtre ?</t>
         </is>
       </c>
     </row>
@@ -6649,6 +6833,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|La plante a de l'eau. Elle a de la lumière. Papa était là. La plante a besoin d'eau et de lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6839,6 +7028,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6863,7 +7057,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Kenzo prend une pomme. Un rire court, tout petit. La pomme est rouge. Papa dit : la plante boit. Eau. Lumière. Adulte. La plante a besoin d'eau et de lumière, avec un adulte.</t>
+          <t>Kenzo prend une pomme. Un rire court, tout petit. La pomme est rouge. La plante boit. Eau. Lumière. Adulte. La plante a besoin d'eau et de lumière, avec un adulte.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7001,6 +7195,13 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend une pomme. Un rire court, tout petit. La pomme est rouge.
+papa|La plante boit. Eau. Lumière. Adulte.
+narrateur|La plante a besoin d'eau et de lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7187,6 +7388,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7211,7 +7417,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Kenzo s'approche de le chat. Le tissu est tout doux. On parle tout bas. On a arrosé. Eau et lumière, avec un adulte. La fenêtre donne la lumière. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo range. Papa dit : c'est bien.</t>
+          <t>Kenzo s'approche de le chat. Le tissu est tout doux. On parle tout bas. On a arrosé. Eau et lumière, avec un adulte. La fenêtre donne la lumière. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo range. C'est bien.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7349,6 +7555,12 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chat. Le tissu est tout doux. On parle tout bas. On a arrosé. Eau et lumière, avec un adulte. La fenêtre donne la lumière. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7511,6 +7723,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7673,6 +7890,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chien. Une cuillère tinte. On range les jouets. On a arrosé. Eau et lumière, avec un adulte. L'arrosoir est rangé. La plante a besoin d'eau et de lumière, avec un adulte. On souffle. Kenzo sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7835,6 +8057,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7997,6 +8224,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de la poule. Le sable est tiède. On s'assoit un moment. On a arrosé. Eau et lumière, avec un adulte. La feuille est plus douce. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8159,6 +8391,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8321,6 +8558,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un yaourt. Un nuage passe lentement. Kenzo pose le yaourt. Une goutte tombe. On arrose avec un adulte. La plante a besoin d'eau et de lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8507,6 +8749,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8669,6 +8916,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chat. Un rire court, tout petit. On respire, un, deux. On a arrosé. Eau et lumière, avec un adulte. La terre est humide. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8831,6 +9083,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8993,6 +9250,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chien. Le papier froisse, chut. On referme le sac. On a arrosé. Eau et lumière, avec un adulte. La fenêtre donne la lumière. La plante a besoin d'eau et de lumière, avec un adulte. Papa serre Kenzo tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9155,6 +9417,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9317,6 +9584,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de la poule. L'herbe chatouille le mollet. On essuie une miette. On a arrosé. Eau et lumière, avec un adulte. L'arrosoir est rangé. La plante a besoin d'eau et de lumière, avec un adulte. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9479,6 +9751,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9641,6 +9918,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un morceau de pain. Un pigeon roucoule. Le pain sent le chaud. La plante sent l'eau. La lumière entre. Adulte près. La plante a besoin d'eau et de lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9827,6 +10109,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9851,7 +10138,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Kenzo s'approche de le chat. Un pigeon roucoule. On met le doudou près. On a arrosé. Eau et lumière, avec un adulte. La feuille est plus douce. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo range. Papa dit : c'est bien.</t>
+          <t>Kenzo s'approche de le chat. Un pigeon roucoule. On met le doudou près. On a arrosé. Eau et lumière, avec un adulte. La feuille est plus douce. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo range. C'est bien.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -9989,6 +10276,12 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chat. Un pigeon roucoule. On met le doudou près. On a arrosé. Eau et lumière, avec un adulte. La feuille est plus douce. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10151,6 +10444,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10313,6 +10611,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chien. La fenêtre vibre un peu. On lace les chaussures. On a arrosé. Eau et lumière, avec un adulte. La terre est humide. La plante a besoin d'eau et de lumière, avec un adulte. On souffle. Kenzo sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10475,6 +10778,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10637,6 +10945,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de la poule. Le lait est froid dans le verre. On met le manteau. On a arrosé. Eau et lumière, avec un adulte. La fenêtre donne la lumière. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10799,6 +11112,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10823,7 +11141,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Kenzo pose une tasse de dînette, vide. Papa dit : pour la plante, on prend l'arrosoir, avec un adulte. Eau. Lumière. Kenzo sourit. La plante a besoin d'eau et de lumière, avec un adulte.</t>
+          <t>Kenzo pose une tasse de dînette, vide. Pour la plante, on prend l'arrosoir, avec un adulte. Eau. Lumière. Kenzo sourit. La plante a besoin d'eau et de lumière, avec un adulte.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10961,6 +11279,13 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo pose une tasse de dînette, vide.
+papa|Pour la plante, on prend l'arrosoir, avec un adulte. Eau. Lumière.
+narrateur|Kenzo sourit. La plante a besoin d'eau et de lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11137,6 +11462,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On arrose. Avec qui ?</t>
         </is>
       </c>
     </row>
@@ -11305,6 +11635,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|On a arrosé avec papa. L'adulte tenait l'arrosoir. La plante a besoin d'eau et de lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11495,6 +11830,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11657,6 +11997,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend une pomme. Le bois sent le chaud. Kenzo montre la pomme, puis la feuille. Eau. Lumière. Avec un adulte. La plante a besoin d'eau et de lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11843,6 +12188,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12005,6 +12355,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chat. La corde du sac est rêche. On boit une gorgée. On a arrosé. Eau et lumière, avec un adulte. L'arrosoir est rangé. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12167,6 +12522,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12329,6 +12689,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chien. Le savon mousse entre les doigts. On feuillette le livre. On a arrosé. Eau et lumière, avec un adulte. La feuille est plus douce. La plante a besoin d'eau et de lumière, avec un adulte. Papa serre Kenzo tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12491,6 +12856,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12653,6 +13023,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de la poule. Un ruisseau chante. On referme le livre. On a arrosé. Eau et lumière, avec un adulte. La terre est humide. La plante a besoin d'eau et de lumière, avec un adulte. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12815,6 +13190,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12977,6 +13357,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un yaourt. Les chaussures font toc toc. Le yaourt est froid. La terre est fraîche. On a arrosé avec un adulte. La plante a besoin d'eau et de lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13163,6 +13548,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13187,7 +13577,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Kenzo s'approche de le chat. La laine gratte un peu. On pose le ballon. On a arrosé. Eau et lumière, avec un adulte. La fenêtre donne la lumière. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo range. Papa dit : c'est bien.</t>
+          <t>Kenzo s'approche de le chat. La laine gratte un peu. On pose le ballon. On a arrosé. Eau et lumière, avec un adulte. La fenêtre donne la lumière. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo range. C'est bien.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13325,6 +13715,12 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chat. La laine gratte un peu. On pose le ballon. On a arrosé. Eau et lumière, avec un adulte. La fenêtre donne la lumière. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13487,6 +13883,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13649,6 +14050,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chien. Un pain croustille. On secoue le sable. On a arrosé. Eau et lumière, avec un adulte. L'arrosoir est rangé. La plante a besoin d'eau et de lumière, avec un adulte. On souffle. Kenzo sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13811,6 +14217,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13973,6 +14384,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de la poule. Le savon glisse. On caresse le tissu. On a arrosé. Eau et lumière, avec un adulte. La feuille est plus douce. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14135,6 +14551,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14297,6 +14718,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un morceau de pain. Le savon sent la fleur. Kenzo range le pain. Papa referme l'arrosoir. Eau, lumière, adulte. La plante a besoin d'eau et de lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14483,6 +14909,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14645,6 +15076,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chat. Une plume vole. On tend la main. On a arrosé. Eau et lumière, avec un adulte. La terre est humide. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14807,6 +15243,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14969,6 +15410,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de le chien. Le banc est lisse. On chante un petit air. On a arrosé. Eau et lumière, avec un adulte. La fenêtre donne la lumière. La plante a besoin d'eau et de lumière, avec un adulte. Papa serre Kenzo tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15131,6 +15577,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15293,6 +15744,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'approche de la poule. Un grelot sonne. On compte jusqu'à trois. On a arrosé. Eau et lumière, avec un adulte. L'arrosoir est rangé. La plante a besoin d'eau et de lumière, avec un adulte. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15455,6 +15911,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15473,7 +15934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15490,6 +15951,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-VIV-004.xlsx
+++ b/stories/arbres/TREE-VIV-004.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Kenzo aide, tout doux. L'eau coule. La lumière entre. La plante a besoin d'eau et de lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1516,6 +1522,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
 narrateur|Kenzo touche la terre. Elle est sèche. On arrose avec papa. La plante a besoin d'eau et de lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1868,6 +1876,7 @@
           <t>narrateur|La plante a soif. On fait quoi ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2039,6 +2048,7 @@
           <t>narrateur|Kenzo a arrosé, avec un adulte. Eau. Lumière. La plante a besoin d'eau et de lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2234,6 +2244,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2401,6 +2412,7 @@
           <t>narrateur|Kenzo prend une pomme. Un vélo passe, toc toc. Kenzo pose une pomme près de la plante. L'eau a coulé. La lumière reste. Avec un adulte. La plante a besoin d'eau et de lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2590,6 +2602,11 @@
       <c r="AW9" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -2759,6 +2776,7 @@
           <t>narrateur|Kenzo s'approche de le chat. La lumière est claire. On range la chaise. On a arrosé. Eau et lumière, avec un adulte. La terre est humide. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2926,6 +2944,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3093,6 +3112,11 @@
           <t>narrateur|Kenzo s'approche de le chien. Des miettes dorment sur la table. On range un objet. On a arrosé. Eau et lumière, avec un adulte. La fenêtre donne la lumière. La plante a besoin d'eau et de lumière, avec un adulte. Papa serre Kenzo tout doux.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3260,6 +3284,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3427,6 +3452,7 @@
           <t>narrateur|Kenzo s'approche de la poule. Un chat miaule une fois. On se tient la main. On a arrosé. Eau et lumière, avec un adulte. L'arrosoir est rangé. La plante a besoin d'eau et de lumière, avec un adulte. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3594,6 +3620,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3761,6 +3788,7 @@
           <t>narrateur|Kenzo prend un yaourt. Le banc est lisse. Un yaourt attend. Kenzo regarde la terre humide. Eau, lumière, adulte. La plante a besoin d'eau et de lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3950,6 +3978,11 @@
       <c r="AW17" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -4120,6 +4153,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4287,6 +4321,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4454,6 +4489,11 @@
           <t>narrateur|Kenzo s'approche de le chien. La couverture est douce. On souffle doucement. On a arrosé. Eau et lumière, avec un adulte. La terre est humide. La plante a besoin d'eau et de lumière, avec un adulte. On souffle. Kenzo sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4621,6 +4661,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4788,6 +4829,7 @@
           <t>narrateur|Kenzo s'approche de la poule. Une cloche tinte au loin. On écoute jusqu'au bout. On a arrosé. Eau et lumière, avec un adulte. La fenêtre donne la lumière. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4955,6 +4997,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5124,6 +5167,7 @@
 narrateur|La lumière est là. La plante a besoin d'eau et de lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5313,6 +5357,11 @@
       <c r="AW25" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -5482,6 +5531,7 @@
           <t>narrateur|Kenzo s'approche de le chat. Le bois sent le chaud. On attend son tour. On a arrosé. Eau et lumière, avec un adulte. L'arrosoir est rangé. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5649,6 +5699,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5816,6 +5867,11 @@
           <t>narrateur|Kenzo s'approche de le chien. Une goutte tombe, ploc. On sourit ensemble. On a arrosé. Eau et lumière, avec un adulte. La feuille est plus douce. La plante a besoin d'eau et de lumière, avec un adulte. Papa serre Kenzo tout doux.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5983,6 +6039,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6150,6 +6207,7 @@
           <t>narrateur|Kenzo s'approche de la poule. Le savon sent la fleur. On pose les pieds par terre. On a arrosé. Eau et lumière, avec un adulte. La terre est humide. La plante a besoin d'eau et de lumière, avec un adulte. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6317,6 +6375,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6484,6 +6543,7 @@
           <t>narrateur|Kenzo ouvre le livre des plantes. Une image verte. Papa montre la fenêtre. La lumière. Puis l'eau, avec un adulte. Kenzo écoute. La plante a besoin d'eau et de lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6667,6 +6727,7 @@
           <t>narrateur|La plante a besoin de quoi, près de la fenêtre ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6838,6 +6899,7 @@
           <t>narrateur|La plante a de l'eau. Elle a de la lumière. Papa était là. La plante a besoin d'eau et de lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7033,6 +7095,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7202,6 +7265,7 @@
 narrateur|La plante a besoin d'eau et de lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7391,6 +7455,11 @@
       <c r="AW37" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -7561,6 +7630,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7728,6 +7798,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7895,6 +7966,11 @@
           <t>narrateur|Kenzo s'approche de le chien. Une cuillère tinte. On range les jouets. On a arrosé. Eau et lumière, avec un adulte. L'arrosoir est rangé. La plante a besoin d'eau et de lumière, avec un adulte. On souffle. Kenzo sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8062,6 +8138,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8229,6 +8306,7 @@
           <t>narrateur|Kenzo s'approche de la poule. Le sable est tiède. On s'assoit un moment. On a arrosé. Eau et lumière, avec un adulte. La feuille est plus douce. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8396,6 +8474,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8563,6 +8642,7 @@
           <t>narrateur|Kenzo prend un yaourt. Un nuage passe lentement. Kenzo pose le yaourt. Une goutte tombe. On arrose avec un adulte. La plante a besoin d'eau et de lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8752,6 +8832,11 @@
       <c r="AW45" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -8921,6 +9006,7 @@
           <t>narrateur|Kenzo s'approche de le chat. Un rire court, tout petit. On respire, un, deux. On a arrosé. Eau et lumière, avec un adulte. La terre est humide. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9088,6 +9174,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9255,6 +9342,11 @@
           <t>narrateur|Kenzo s'approche de le chien. Le papier froisse, chut. On referme le sac. On a arrosé. Eau et lumière, avec un adulte. La fenêtre donne la lumière. La plante a besoin d'eau et de lumière, avec un adulte. Papa serre Kenzo tout doux.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9422,6 +9514,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9589,6 +9682,7 @@
           <t>narrateur|Kenzo s'approche de la poule. L'herbe chatouille le mollet. On essuie une miette. On a arrosé. Eau et lumière, avec un adulte. L'arrosoir est rangé. La plante a besoin d'eau et de lumière, avec un adulte. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9756,6 +9850,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9923,6 +10018,7 @@
           <t>narrateur|Kenzo prend un morceau de pain. Un pigeon roucoule. Le pain sent le chaud. La plante sent l'eau. La lumière entre. Adulte près. La plante a besoin d'eau et de lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10112,6 +10208,11 @@
       <c r="AW53" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -10282,6 +10383,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10449,6 +10551,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10616,6 +10719,11 @@
           <t>narrateur|Kenzo s'approche de le chien. La fenêtre vibre un peu. On lace les chaussures. On a arrosé. Eau et lumière, avec un adulte. La terre est humide. La plante a besoin d'eau et de lumière, avec un adulte. On souffle. Kenzo sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10783,6 +10891,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10950,6 +11059,7 @@
           <t>narrateur|Kenzo s'approche de la poule. Le lait est froid dans le verre. On met le manteau. On a arrosé. Eau et lumière, avec un adulte. La fenêtre donne la lumière. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11117,6 +11227,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11286,6 +11397,7 @@
 narrateur|Kenzo sourit. La plante a besoin d'eau et de lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11469,6 +11581,7 @@
           <t>narrateur|On arrose. Avec qui ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11640,6 +11753,7 @@
           <t>narrateur|On a arrosé avec papa. L'adulte tenait l'arrosoir. La plante a besoin d'eau et de lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11835,6 +11949,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12002,6 +12117,7 @@
           <t>narrateur|Kenzo prend une pomme. Le bois sent le chaud. Kenzo montre la pomme, puis la feuille. Eau. Lumière. Avec un adulte. La plante a besoin d'eau et de lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12191,6 +12307,11 @@
       <c r="AW65" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -12360,6 +12481,7 @@
           <t>narrateur|Kenzo s'approche de le chat. La corde du sac est rêche. On boit une gorgée. On a arrosé. Eau et lumière, avec un adulte. L'arrosoir est rangé. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12527,6 +12649,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12694,6 +12817,11 @@
           <t>narrateur|Kenzo s'approche de le chien. Le savon mousse entre les doigts. On feuillette le livre. On a arrosé. Eau et lumière, avec un adulte. La feuille est plus douce. La plante a besoin d'eau et de lumière, avec un adulte. Papa serre Kenzo tout doux.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12861,6 +12989,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13028,6 +13157,7 @@
           <t>narrateur|Kenzo s'approche de la poule. Un ruisseau chante. On referme le livre. On a arrosé. Eau et lumière, avec un adulte. La terre est humide. La plante a besoin d'eau et de lumière, avec un adulte. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13195,6 +13325,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13362,6 +13493,7 @@
           <t>narrateur|Kenzo prend un yaourt. Les chaussures font toc toc. Le yaourt est froid. La terre est fraîche. On a arrosé avec un adulte. La plante a besoin d'eau et de lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13551,6 +13683,11 @@
       <c r="AW73" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -13721,6 +13858,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13888,6 +14026,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14055,6 +14194,11 @@
           <t>narrateur|Kenzo s'approche de le chien. Un pain croustille. On secoue le sable. On a arrosé. Eau et lumière, avec un adulte. L'arrosoir est rangé. La plante a besoin d'eau et de lumière, avec un adulte. On souffle. Kenzo sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14222,6 +14366,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14389,6 +14534,7 @@
           <t>narrateur|Kenzo s'approche de la poule. Le savon glisse. On caresse le tissu. On a arrosé. Eau et lumière, avec un adulte. La feuille est plus douce. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14556,6 +14702,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14723,6 +14870,7 @@
           <t>narrateur|Kenzo prend un morceau de pain. Le savon sent la fleur. Kenzo range le pain. Papa referme l'arrosoir. Eau, lumière, adulte. La plante a besoin d'eau et de lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14912,6 +15060,11 @@
       <c r="AW81" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -15081,6 +15234,7 @@
           <t>narrateur|Kenzo s'approche de le chat. Une plume vole. On tend la main. On a arrosé. Eau et lumière, avec un adulte. La terre est humide. La plante a besoin d'eau et de lumière, avec un adulte. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15248,6 +15402,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15415,6 +15570,11 @@
           <t>narrateur|Kenzo s'approche de le chien. Le banc est lisse. On chante un petit air. On a arrosé. Eau et lumière, avec un adulte. La fenêtre donne la lumière. La plante a besoin d'eau et de lumière, avec un adulte. Papa serre Kenzo tout doux.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15582,6 +15742,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15749,6 +15910,7 @@
           <t>narrateur|Kenzo s'approche de la poule. Un grelot sonne. On compte jusqu'à trois. On a arrosé. Eau et lumière, avec un adulte. L'arrosoir est rangé. La plante a besoin d'eau et de lumière, avec un adulte. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15916,6 +16078,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15934,7 +16097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15958,6 +16121,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15972,7 +16149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16159,6 +16336,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
